--- a/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_11_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_11_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO JORGE ISAACS (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_11_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL_11_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,11 +6285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6385,7 +6293,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,11 +6534,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6638,7 +6542,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -6887,7 +6787,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7128,11 +7028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7140,7 +7036,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7381,11 +7277,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7393,7 +7285,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7634,11 +7526,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7646,7 +7534,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7887,11 +7775,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -7899,7 +7783,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8140,11 +8024,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8152,7 +8032,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8393,11 +8273,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8405,7 +8281,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8646,11 +8522,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8658,7 +8530,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8899,11 +8771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -8911,7 +8779,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9152,11 +9020,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9164,7 +9028,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9405,11 +9269,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9417,7 +9277,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9658,11 +9518,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9670,7 +9526,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9911,11 +9767,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -9923,7 +9775,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10164,11 +10016,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800384</t>
@@ -10176,7 +10024,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO JORGE ISAACS (IED)</t>
+          <t>COLEGIO JORGE ISAACS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
